--- a/exports/trend_1d/TATACONSUM_full_report.xlsx
+++ b/exports/trend_1d/TATACONSUM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,25 +557,25 @@
         <v>6.98</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="H2" t="n">
-        <v>150.55</v>
+        <v>147.7</v>
       </c>
       <c r="I2" t="n">
         <v>147.9221705718</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.08</v>
+        <v>-3.93</v>
       </c>
       <c r="L2" t="n">
-        <v>2.63</v>
+        <v>4.49</v>
       </c>
       <c r="M2" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="N2" t="n">
         <v>2.39</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.11</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42103</v>
+        <v>42104</v>
       </c>
       <c r="H3" t="n">
-        <v>150.2</v>
+        <v>159.2</v>
       </c>
       <c r="I3" t="n">
         <v>156.2460043976265</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.69</v>
+        <v>-7.79</v>
       </c>
       <c r="L3" t="n">
         <v>10.29</v>
@@ -612,7 +647,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>3.29</v>
+        <v>5.99</v>
       </c>
       <c r="O3" t="n">
         <v>-1.89</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.05</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42117</v>
+        <v>42118</v>
       </c>
       <c r="H4" t="n">
-        <v>148.35</v>
+        <v>145.45</v>
       </c>
       <c r="I4" t="n">
         <v>146.5282442564753</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.82</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="L4" t="n">
         <v>9.52</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>9.94</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42202</v>
+        <v>42205</v>
       </c>
       <c r="H5" t="n">
-        <v>137.3</v>
+        <v>140</v>
       </c>
       <c r="I5" t="n">
         <v>138.6108736255686</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K5" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
         <v>2.3</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42228</v>
+        <v>42229</v>
       </c>
       <c r="H6" t="n">
-        <v>131.4</v>
+        <v>128.4</v>
       </c>
       <c r="I6" t="n">
         <v>130.8583355201377</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K6" t="n">
-        <v>-6.14</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>6.79</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="M6" t="n">
         <v>1.14</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.4</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42283</v>
+        <v>42284</v>
       </c>
       <c r="H7" t="n">
-        <v>128.95</v>
+        <v>131.4</v>
       </c>
       <c r="I7" t="n">
         <v>130.5984396113166</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.43</v>
+        <v>-2.34</v>
       </c>
       <c r="L7" t="n">
         <v>4.95</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>8.35</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42312</v>
+        <v>42313</v>
       </c>
       <c r="H8" t="n">
-        <v>130.15</v>
+        <v>126.45</v>
       </c>
       <c r="I8" t="n">
         <v>127.061233003639</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.95</v>
+        <v>-3.77</v>
       </c>
       <c r="L8" t="n">
-        <v>1.67</v>
+        <v>4.15</v>
       </c>
       <c r="M8" t="n">
         <v>0.3</v>
       </c>
       <c r="N8" t="n">
-        <v>2.22</v>
+        <v>2.84</v>
       </c>
       <c r="O8" t="n">
         <v>1.9</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>10.06</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42335</v>
+        <v>42338</v>
       </c>
       <c r="H9" t="n">
-        <v>135.25</v>
+        <v>135.85</v>
       </c>
       <c r="I9" t="n">
         <v>135.6520912794122</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.96</v>
+        <v>-7.43</v>
       </c>
       <c r="L9" t="n">
         <v>8.109999999999999</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>8.18</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42381</v>
+        <v>42382</v>
       </c>
       <c r="H10" t="n">
-        <v>137.8</v>
+        <v>133.95</v>
       </c>
       <c r="I10" t="n">
         <v>134.4729255496307</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K10" t="n">
-        <v>1.44</v>
+        <v>-1.4</v>
       </c>
       <c r="L10" t="n">
-        <v>5.19</v>
+        <v>5.26</v>
       </c>
       <c r="M10" t="n">
         <v>0.95</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>12.2</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42446</v>
+        <v>42447</v>
       </c>
       <c r="H11" t="n">
-        <v>114.4</v>
+        <v>117.45</v>
       </c>
       <c r="I11" t="n">
         <v>117.2304225371872</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K11" t="n">
-        <v>14.59</v>
+        <v>12.32</v>
       </c>
       <c r="L11" t="n">
         <v>4.67</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42669</v>
+        <v>42670</v>
       </c>
       <c r="H12" t="n">
-        <v>143.6</v>
+        <v>136.05</v>
       </c>
       <c r="I12" t="n">
         <v>137.317447787607</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K12" t="n">
-        <v>22.26</v>
+        <v>15.84</v>
       </c>
       <c r="L12" t="n">
         <v>3.28</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>148</v>
+        <v>149</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>8</v>
+      </c>
+      <c r="U12" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>12.94</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42745</v>
+        <v>42746</v>
       </c>
       <c r="H13" t="n">
-        <v>122.9</v>
+        <v>126</v>
       </c>
       <c r="I13" t="n">
         <v>125.0225922641222</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K13" t="n">
-        <v>9.67</v>
+        <v>7.39</v>
       </c>
       <c r="L13" t="n">
         <v>2.57</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.17</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42877</v>
+        <v>42878</v>
       </c>
       <c r="H14" t="n">
-        <v>146</v>
+        <v>142.95</v>
       </c>
       <c r="I14" t="n">
         <v>143.9679443609319</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K14" t="n">
-        <v>15.87</v>
+        <v>13.45</v>
       </c>
       <c r="L14" t="n">
         <v>2.74</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42892</v>
+        <v>42893</v>
       </c>
       <c r="H15" t="n">
-        <v>151.1</v>
+        <v>153.65</v>
       </c>
       <c r="I15" t="n">
         <v>153.267314736203</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.7</v>
+        <v>-7.49</v>
       </c>
       <c r="L15" t="n">
         <v>9.41</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>8.76</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42956</v>
+        <v>42957</v>
       </c>
       <c r="H16" t="n">
-        <v>160.1</v>
+        <v>154.1</v>
       </c>
       <c r="I16" t="n">
         <v>157.6115317539981</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>0.29</v>
       </c>
       <c r="L16" t="n">
         <v>6.31</v>
@@ -1353,7 +1544,7 @@
         <v>1.15</v>
       </c>
       <c r="N16" t="n">
-        <v>2.61</v>
+        <v>3.75</v>
       </c>
       <c r="O16" t="n">
         <v>1.69</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>12.26</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42958</v>
+        <v>42961</v>
       </c>
       <c r="H17" t="n">
-        <v>162.2</v>
+        <v>176.55</v>
       </c>
       <c r="I17" t="n">
         <v>172.985473967849</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.26</v>
+        <v>-14.57</v>
       </c>
       <c r="L17" t="n">
-        <v>5.65</v>
+        <v>15.57</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>5.26</v>
+        <v>8.85</v>
       </c>
       <c r="O17" t="n">
         <v>-3.75</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>15.62</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H18" t="n">
-        <v>198.7</v>
+        <v>194.25</v>
       </c>
       <c r="I18" t="n">
         <v>194.8817043060802</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K18" t="n">
-        <v>12.55</v>
+        <v>10.03</v>
       </c>
       <c r="L18" t="n">
         <v>7.65</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>11.15</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43034</v>
+        <v>43035</v>
       </c>
       <c r="H19" t="n">
-        <v>207.2</v>
+        <v>217.8</v>
       </c>
       <c r="I19" t="n">
         <v>215.9123913047808</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.67</v>
+        <v>-12.12</v>
       </c>
       <c r="L19" t="n">
-        <v>9.83</v>
+        <v>12.79</v>
       </c>
       <c r="M19" t="n">
         <v>0.89</v>
       </c>
       <c r="N19" t="n">
-        <v>4.07</v>
+        <v>5.12</v>
       </c>
       <c r="O19" t="n">
         <v>-2.24</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>11.49</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43125</v>
+        <v>43129</v>
       </c>
       <c r="H20" t="n">
-        <v>300.5</v>
+        <v>298.1</v>
       </c>
       <c r="I20" t="n">
         <v>298.1521242055948</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K20" t="n">
-        <v>37.97</v>
+        <v>36.87</v>
       </c>
       <c r="L20" t="n">
         <v>4.89</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.17</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43206</v>
+        <v>43207</v>
       </c>
       <c r="H21" t="n">
-        <v>276.2</v>
+        <v>277.5</v>
       </c>
       <c r="I21" t="n">
         <v>276.890194686662</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K21" t="n">
-        <v>7.35</v>
+        <v>6.91</v>
       </c>
       <c r="L21" t="n">
         <v>1.83</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>7.92</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43231</v>
+        <v>43234</v>
       </c>
       <c r="H22" t="n">
-        <v>283.95</v>
+        <v>252.75</v>
       </c>
       <c r="I22" t="n">
         <v>272.3263401437234</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>2.32</v>
+        <v>-8.92</v>
       </c>
       <c r="L22" t="n">
-        <v>1.23</v>
+        <v>10.36</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3</v>
+        <v>2.61</v>
       </c>
       <c r="N22" t="n">
-        <v>2.31</v>
+        <v>10.99</v>
       </c>
       <c r="O22" t="n">
         <v>0.47</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>16.29</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43264</v>
+        <v>43265</v>
       </c>
       <c r="H23" t="n">
-        <v>266.3</v>
+        <v>274.4</v>
       </c>
       <c r="I23" t="n">
         <v>270.7363802934871</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.36</v>
+        <v>-8.57</v>
       </c>
       <c r="L23" t="n">
         <v>9.949999999999999</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>10.57</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43294</v>
+        <v>43297</v>
       </c>
       <c r="H24" t="n">
-        <v>255.7</v>
+        <v>240.25</v>
       </c>
       <c r="I24" t="n">
         <v>248.0959920450588</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K24" t="n">
-        <v>-6.81</v>
+        <v>-12.45</v>
       </c>
       <c r="L24" t="n">
-        <v>8.039999999999999</v>
+        <v>12.85</v>
       </c>
       <c r="M24" t="n">
         <v>1.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.02</v>
+        <v>6.04</v>
       </c>
       <c r="O24" t="n">
         <v>3.04</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>14.44</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43535</v>
+        <v>43536</v>
       </c>
       <c r="H25" t="n">
-        <v>200</v>
+        <v>202.4</v>
       </c>
       <c r="I25" t="n">
         <v>201.5524862695455</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K25" t="n">
-        <v>16.75</v>
+        <v>15.75</v>
       </c>
       <c r="L25" t="n">
         <v>6.04</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>160</v>
+        <v>161</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>9</v>
+      </c>
+      <c r="U25" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>8.66</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43591</v>
+        <v>43592</v>
       </c>
       <c r="H26" t="n">
-        <v>200.15</v>
+        <v>197.3</v>
       </c>
       <c r="I26" t="n">
         <v>198.0767202849111</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.11</v>
+        <v>-2.52</v>
       </c>
       <c r="L26" t="n">
         <v>5.53</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>10.13</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43600</v>
+        <v>43601</v>
       </c>
       <c r="H27" t="n">
-        <v>196.8</v>
+        <v>218.1</v>
       </c>
       <c r="I27" t="n">
         <v>212.4943619988084</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" t="n">
-        <v>0.25</v>
+        <v>-10.54</v>
       </c>
       <c r="L27" t="n">
-        <v>3.12</v>
+        <v>11.63</v>
       </c>
       <c r="M27" t="n">
-        <v>1.06</v>
+        <v>3.89</v>
       </c>
       <c r="N27" t="n">
-        <v>0.6899999999999999</v>
+        <v>10.82</v>
       </c>
       <c r="O27" t="n">
         <v>-1.42</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>15.69</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43664</v>
+        <v>43665</v>
       </c>
       <c r="H28" t="n">
-        <v>251.95</v>
+        <v>245.8</v>
       </c>
       <c r="I28" t="n">
         <v>247.0133527398768</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K28" t="n">
-        <v>15.52</v>
+        <v>12.7</v>
       </c>
       <c r="L28" t="n">
         <v>10.71</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>9.9</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43704</v>
+        <v>43705</v>
       </c>
       <c r="H29" t="n">
-        <v>263.15</v>
+        <v>276.6</v>
       </c>
       <c r="I29" t="n">
         <v>267.5516669847866</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K29" t="n">
-        <v>-7.06</v>
+        <v>-12.53</v>
       </c>
       <c r="L29" t="n">
-        <v>10.25</v>
+        <v>13.04</v>
       </c>
       <c r="M29" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="N29" t="n">
-        <v>3.71</v>
+        <v>5.11</v>
       </c>
       <c r="O29" t="n">
         <v>-2.44</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>10.9</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43888</v>
+        <v>43889</v>
       </c>
       <c r="H30" t="n">
-        <v>358.85</v>
+        <v>341.9</v>
       </c>
       <c r="I30" t="n">
         <v>357.9208029953085</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K30" t="n">
-        <v>29.74</v>
+        <v>23.61</v>
       </c>
       <c r="L30" t="n">
         <v>10.74</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1</v>
+        <v>1.48</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>4.72</v>
       </c>
       <c r="O30" t="n">
         <v>5.11</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>8</v>
+      </c>
+      <c r="U30" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>11.14</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43934</v>
+        <v>43936</v>
       </c>
       <c r="H31" t="n">
-        <v>301.3</v>
+        <v>311.75</v>
       </c>
       <c r="I31" t="n">
         <v>310.913185858062</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K31" t="n">
-        <v>11.87</v>
+        <v>8.82</v>
       </c>
       <c r="L31" t="n">
         <v>3.41</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>21.77</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44092</v>
+        <v>44095</v>
       </c>
       <c r="H32" t="n">
-        <v>533.95</v>
+        <v>501.5</v>
       </c>
       <c r="I32" t="n">
         <v>515.3131437095115</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="K32" t="n">
-        <v>71.28</v>
+        <v>60.87</v>
       </c>
       <c r="L32" t="n">
         <v>3.37</v>
@@ -2265,7 +2648,7 @@
         <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>4.74</v>
+        <v>6.08</v>
       </c>
       <c r="O32" t="n">
         <v>3.47</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>6</v>
+      </c>
+      <c r="U32" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>13.62</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44148</v>
+        <v>44149</v>
       </c>
       <c r="H33" t="n">
-        <v>506.95</v>
+        <v>509.8</v>
       </c>
       <c r="I33" t="n">
         <v>508.2956589036097</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.09</v>
+        <v>-1.66</v>
       </c>
       <c r="L33" t="n">
         <v>6.81</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.14</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44218</v>
+        <v>44221</v>
       </c>
       <c r="H34" t="n">
-        <v>577.55</v>
+        <v>566.55</v>
       </c>
       <c r="I34" t="n">
         <v>572.2076909253851</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K34" t="n">
-        <v>13.29</v>
+        <v>11.13</v>
       </c>
       <c r="L34" t="n">
         <v>2.15</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>10.77</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44239</v>
+        <v>44242</v>
       </c>
       <c r="H35" t="n">
-        <v>600.05</v>
+        <v>615.45</v>
       </c>
       <c r="I35" t="n">
         <v>612.1082986973187</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.91</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>8.44</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M35" t="n">
         <v>2.37</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44466</v>
+        <v>44467</v>
       </c>
       <c r="H36" t="n">
-        <v>824.8</v>
+        <v>812.6</v>
       </c>
       <c r="I36" t="n">
         <v>820.9326510495501</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K36" t="n">
-        <v>34.02</v>
+        <v>32.03</v>
       </c>
       <c r="L36" t="n">
         <v>7.39</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>152</v>
+        <v>153</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>8</v>
+      </c>
+      <c r="U36" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>6.36</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44634</v>
+        <v>44635</v>
       </c>
       <c r="H37" t="n">
-        <v>713.4</v>
+        <v>739.4</v>
       </c>
       <c r="I37" t="n">
         <v>727.8770557819073</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K37" t="n">
-        <v>12.21</v>
+        <v>9.01</v>
       </c>
       <c r="L37" t="n">
         <v>4.9</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>7</v>
+      </c>
+      <c r="U37" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>10.75</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44687</v>
+        <v>44690</v>
       </c>
       <c r="H38" t="n">
-        <v>755.55</v>
+        <v>748.95</v>
       </c>
       <c r="I38" t="n">
         <v>751.782731570958</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K38" t="n">
-        <v>2.18</v>
+        <v>1.29</v>
       </c>
       <c r="L38" t="n">
         <v>5.34</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44756</v>
+        <v>44757</v>
       </c>
       <c r="H39" t="n">
-        <v>756.45</v>
+        <v>780.85</v>
       </c>
       <c r="I39" t="n">
         <v>761.7287645223201</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K39" t="n">
-        <v>-1</v>
+        <v>-4.26</v>
       </c>
       <c r="L39" t="n">
-        <v>2.93</v>
+        <v>4.53</v>
       </c>
       <c r="M39" t="n">
         <v>1.9</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>8.24</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44784</v>
+        <v>44785</v>
       </c>
       <c r="H40" t="n">
-        <v>763.95</v>
+        <v>754.1</v>
       </c>
       <c r="I40" t="n">
         <v>756.8302744631048</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.16</v>
+        <v>-3.43</v>
       </c>
       <c r="L40" t="n">
-        <v>3.07</v>
+        <v>3.8</v>
       </c>
       <c r="M40" t="n">
         <v>2.52</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>7.22</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44803</v>
+        <v>44805</v>
       </c>
       <c r="H41" t="n">
-        <v>799.7</v>
+        <v>828.1</v>
       </c>
       <c r="I41" t="n">
         <v>808.5324527481479</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K41" t="n">
-        <v>-6.05</v>
+        <v>-9.81</v>
       </c>
       <c r="L41" t="n">
-        <v>6.97</v>
+        <v>10.28</v>
       </c>
       <c r="M41" t="n">
         <v>0.51</v>
       </c>
       <c r="N41" t="n">
-        <v>2.1</v>
+        <v>3.55</v>
       </c>
       <c r="O41" t="n">
         <v>-1.29</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>8.73</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H42" t="n">
-        <v>793.35</v>
+        <v>771.95</v>
       </c>
       <c r="I42" t="n">
         <v>782.5612755628055</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.2</v>
+        <v>-6.78</v>
       </c>
       <c r="L42" t="n">
-        <v>6.09</v>
+        <v>7.02</v>
       </c>
       <c r="M42" t="n">
         <v>0.72</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>9.48</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44894</v>
+        <v>44895</v>
       </c>
       <c r="H43" t="n">
-        <v>795.15</v>
+        <v>808</v>
       </c>
       <c r="I43" t="n">
         <v>798.0686794002311</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.01</v>
+        <v>-4.67</v>
       </c>
       <c r="L43" t="n">
-        <v>3.89</v>
+        <v>5.17</v>
       </c>
       <c r="M43" t="n">
         <v>2.3</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.4</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44924</v>
+        <v>44925</v>
       </c>
       <c r="H44" t="n">
-        <v>766.55</v>
+        <v>757.55</v>
       </c>
       <c r="I44" t="n">
         <v>764.1189405897032</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K44" t="n">
-        <v>-5.13</v>
+        <v>-6.24</v>
       </c>
       <c r="L44" t="n">
         <v>6.71</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>6.28</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45019</v>
+        <v>45021</v>
       </c>
       <c r="H45" t="n">
-        <v>708.25</v>
+        <v>718.45</v>
       </c>
       <c r="I45" t="n">
         <v>717.9079946845102</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K45" t="n">
-        <v>6.51</v>
+        <v>5.16</v>
       </c>
       <c r="L45" t="n">
         <v>2</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>5.4</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45369</v>
+        <v>45370</v>
       </c>
       <c r="H46" t="n">
-        <v>1172.4</v>
+        <v>1132.2</v>
       </c>
       <c r="I46" t="n">
         <v>1144.534162416182</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K46" t="n">
-        <v>63.18</v>
+        <v>57.59</v>
       </c>
       <c r="L46" t="n">
         <v>4.25</v>
@@ -3063,7 +3614,7 @@
         <v>2.66</v>
       </c>
       <c r="N46" t="n">
-        <v>3.24</v>
+        <v>3.43</v>
       </c>
       <c r="O46" t="n">
         <v>1.44</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>238</v>
+        <v>239</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>12</v>
+      </c>
+      <c r="U46" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>10.65</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45447</v>
+        <v>45448</v>
       </c>
       <c r="H47" t="n">
-        <v>1073.65</v>
+        <v>1128.35</v>
       </c>
       <c r="I47" t="n">
         <v>1117.63525339865</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K47" t="n">
-        <v>5.17</v>
+        <v>0.34</v>
       </c>
       <c r="L47" t="n">
         <v>3.37</v>
       </c>
       <c r="M47" t="n">
-        <v>1.52</v>
+        <v>2.03</v>
       </c>
       <c r="N47" t="n">
-        <v>4.07</v>
+        <v>5.09</v>
       </c>
       <c r="O47" t="n">
         <v>-3.43</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H48" t="n">
-        <v>1196.25</v>
+        <v>1152.75</v>
       </c>
       <c r="I48" t="n">
         <v>1157.629261317732</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K48" t="n">
-        <v>6.02</v>
+        <v>2.16</v>
       </c>
       <c r="L48" t="n">
         <v>5.71</v>
@@ -3177,7 +3752,7 @@
         <v>1.48</v>
       </c>
       <c r="N48" t="n">
-        <v>2.04</v>
+        <v>3.64</v>
       </c>
       <c r="O48" t="n">
         <v>5.09</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>7.77</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="H49" t="n">
-        <v>955</v>
+        <v>961.6</v>
       </c>
       <c r="I49" t="n">
         <v>960.6802223607416</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K49" t="n">
-        <v>17.15</v>
+        <v>16.58</v>
       </c>
       <c r="L49" t="n">
         <v>3.23</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.75</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45716</v>
+        <v>45719</v>
       </c>
       <c r="H50" t="n">
-        <v>963.7</v>
+        <v>953.9</v>
       </c>
       <c r="I50" t="n">
         <v>958.1652002152449</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K50" t="n">
-        <v>0.22</v>
+        <v>-0.8</v>
       </c>
       <c r="L50" t="n">
         <v>3.7</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45748</v>
+        <v>45749</v>
       </c>
       <c r="H51" t="n">
-        <v>992.25</v>
+        <v>1062.7</v>
       </c>
       <c r="I51" t="n">
         <v>1005.938351096566</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.02</v>
+        <v>-11.41</v>
       </c>
       <c r="L51" t="n">
-        <v>6.41</v>
+        <v>12.5</v>
       </c>
       <c r="M51" t="n">
-        <v>0.88</v>
+        <v>2.6</v>
       </c>
       <c r="N51" t="n">
-        <v>2.91</v>
+        <v>7.1</v>
       </c>
       <c r="O51" t="n">
         <v>-1.02</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>9.81</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45824</v>
+        <v>45825</v>
       </c>
       <c r="H52" t="n">
-        <v>1083.4</v>
+        <v>1071.6</v>
       </c>
       <c r="I52" t="n">
         <v>1076.569265799466</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K52" t="n">
-        <v>1.95</v>
+        <v>0.84</v>
       </c>
       <c r="L52" t="n">
         <v>4.49</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>6.6</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45833</v>
+        <v>45834</v>
       </c>
       <c r="H53" t="n">
-        <v>1126.5</v>
+        <v>1145.4</v>
       </c>
       <c r="I53" t="n">
         <v>1128.803244359861</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K53" t="n">
-        <v>-5.12</v>
+        <v>-6.89</v>
       </c>
       <c r="L53" t="n">
-        <v>5.81</v>
+        <v>7.32</v>
       </c>
       <c r="M53" t="n">
         <v>0.23</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>6.75</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45860</v>
+        <v>45861</v>
       </c>
       <c r="H54" t="n">
-        <v>1084.8</v>
+        <v>1062.6</v>
       </c>
       <c r="I54" t="n">
         <v>1068.117839414151</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K54" t="n">
-        <v>-5.29</v>
+        <v>-7.23</v>
       </c>
       <c r="L54" t="n">
-        <v>6.8</v>
+        <v>8.24</v>
       </c>
       <c r="M54" t="n">
         <v>0.46</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>6.67</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="H55" t="n">
-        <v>1092.1</v>
+        <v>1136.3</v>
       </c>
       <c r="I55" t="n">
         <v>1112.21697156706</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.78</v>
+        <v>-6.94</v>
       </c>
       <c r="L55" t="n">
-        <v>5.97</v>
+        <v>7.17</v>
       </c>
       <c r="M55" t="n">
         <v>2.01</v>
       </c>
       <c r="N55" t="n">
-        <v>2.33</v>
+        <v>4.05</v>
       </c>
       <c r="O55" t="n">
         <v>-2.05</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.44</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="H56" t="n">
-        <v>1187.4</v>
+        <v>1131.8</v>
       </c>
       <c r="I56" t="n">
         <v>1147.895426515889</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K56" t="n">
-        <v>4.5</v>
+        <v>-0.4</v>
       </c>
       <c r="L56" t="n">
         <v>2.93</v>
@@ -3633,7 +4304,7 @@
         <v>2.35</v>
       </c>
       <c r="N56" t="n">
-        <v>2.1</v>
+        <v>4.68</v>
       </c>
       <c r="O56" t="n">
         <v>4.05</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>6</v>
+      </c>
+      <c r="U56" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>10.78</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="H57" t="n">
-        <v>1102.6</v>
+        <v>1113.2</v>
       </c>
       <c r="I57" t="n">
         <v>1106.680375567027</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K57" t="n">
-        <v>2.58</v>
+        <v>1.64</v>
       </c>
       <c r="L57" t="n">
         <v>5.38</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.71</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="H58" t="n">
-        <v>1178.4</v>
+        <v>1143.3</v>
       </c>
       <c r="I58" t="n">
         <v>1158.958885113017</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K58" t="n">
-        <v>5.86</v>
+        <v>2.7</v>
       </c>
       <c r="L58" t="n">
         <v>1.99</v>
@@ -3747,7 +4442,7 @@
         <v>0.89</v>
       </c>
       <c r="N58" t="n">
-        <v>2.17</v>
+        <v>2.98</v>
       </c>
       <c r="O58" t="n">
         <v>0.96</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3807,6 +4514,14 @@
       <c r="Q59" t="n">
         <v>104</v>
       </c>
+      <c r="R59" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8765,7 +9480,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71.3</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -8775,7 +9490,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -8785,7 +9500,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8">
@@ -8795,7 +9510,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -8805,7 +9520,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -8815,7 +9530,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>160.4</v>
+        <v>162.6</v>
       </c>
     </row>
     <row r="11">
@@ -8825,7 +9540,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -8835,7 +9550,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -8845,7 +9560,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33.3</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="14">
@@ -8855,7 +9570,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.06</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="15">
@@ -8865,7 +9580,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10.47</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="16">
@@ -8875,7 +9590,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.49</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="17">
@@ -8885,7 +9600,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>71.28</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="18">
@@ -8895,7 +9610,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.4</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="19">
@@ -8905,7 +9620,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.43</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="20">
@@ -8915,7 +9630,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.34</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="21">
@@ -8925,7 +9640,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.74</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="22">
@@ -8935,7 +9650,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
@@ -8945,7 +9660,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -8955,7 +9670,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="25">
@@ -8975,7 +9690,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.66</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="27">
@@ -8995,7 +9710,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
